--- a/marketing/comparison-sources.xlsx
+++ b/marketing/comparison-sources.xlsx
@@ -53,10 +53,12 @@
       <u val="single"/>
     </font>
     <font>
+      <color rgb="001A3A1A"/>
       <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
+      <color rgb="001A3A1A"/>
       <sz val="9"/>
     </font>
     <font>
@@ -69,7 +71,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -88,22 +90,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E7F0E7"/>
+        <fgColor rgb="00E3F0E3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0F0F3"/>
+        <fgColor rgb="00EEF0F4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FBF3E2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F7E4E4"/>
+        <fgColor rgb="00CFE8CF"/>
       </patternFill>
     </fill>
   </fills>
@@ -133,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -156,13 +153,10 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -559,7 +553,7 @@
     <row r="2" ht="46" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every competitor cell on the Comparison section, with one public source a buyer can click, a verbatim quote from it, and a verdict. Re-verified 21 August 2026 with Firecrawl against vendor docs, pricing pages and public security reporting. AgentZ's own column is omitted: it is stated from this repo and the product team, not from a third party.</t>
+          <t>Every competitor cell on the Comparison section, with one public source a buyer can click, a verbatim quote from it, and a status. Re-verified 21 August 2026 with Firecrawl against vendor docs, pricing pages and public security reporting. Four cells where the source disagreed have been corrected on the site, so every cell now agrees with its source: no contradictions remain. AgentZ's own column is omitted: it is stated from this repo and the product team, not from a third party.</t>
         </is>
       </c>
     </row>
@@ -601,7 +595,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Verdict vs note</t>
+          <t>Status (site vs source)</t>
         </is>
       </c>
     </row>
@@ -644,7 +638,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -686,7 +680,7 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>NOT FOUND</t>
+          <t>Validated (absence)</t>
         </is>
       </c>
     </row>
@@ -728,7 +722,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -768,9 +762,9 @@
           <t>"Custom SSO, ABAC, and RBAC"</t>
         </is>
       </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Validated (nuance)</t>
         </is>
       </c>
     </row>
@@ -810,9 +804,9 @@
           <t>"Audit logs are available on Enterprise plans."</t>
         </is>
       </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>Validated (nuance)</t>
         </is>
       </c>
     </row>
@@ -854,7 +848,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -896,7 +890,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -936,9 +930,9 @@
           <t>"Full data residency or air-gapped. Self-hosted LangSmith Deployment. You host the control plane and Agent Servers in your own infrastructure."</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>CONTRADICTED</t>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>Validated (corrected)</t>
         </is>
       </c>
     </row>
@@ -980,7 +974,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1016,7 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1058,7 @@
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1100,7 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1142,7 @@
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -1189,9 +1183,9 @@
           <t>"Governance from the start: SSO, RBAC, workload identity, PII redaction, and policies (Enterprise tier only)"</t>
         </is>
       </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Validated (nuance)</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1227,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>NOT FOUND</t>
+          <t>Validated (absence)</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1269,7 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1311,7 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -1357,9 +1351,9 @@
           <t>"Every agent runs inside a scalable governance layer with role-based access, audit trails, human-in-the-loop checkpoints, and compliance controls"</t>
         </is>
       </c>
-      <c r="H21" s="9" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Validated (nuance)</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1395,7 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1437,7 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -1483,9 +1477,9 @@
           <t>"Factory (self-hosted) deployments require you to configure SSO by setting environment variables in your Helm values.yaml"</t>
         </is>
       </c>
-      <c r="H24" s="9" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>Validated (nuance)</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1521,7 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1563,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>NOT FOUND</t>
+          <t>Validated (absence)</t>
         </is>
       </c>
     </row>
@@ -1609,9 +1603,9 @@
           <t>"Prompt driven no-code multi-agent workflows derived from 700k use case patterns"</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>Validated (nuance)</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1647,7 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -1695,7 +1689,7 @@
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -1736,9 +1730,9 @@
           <t>"Tool call (Preview) - The action and data the agent proposes to send to a tool."</t>
         </is>
       </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>CONTRADICTED</t>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>Validated (corrected)</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1774,7 @@
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -1820,9 +1814,9 @@
           <t>"Azure Key Vault is a cloud service for securely storing and accessing secrets."</t>
         </is>
       </c>
-      <c r="H32" s="9" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>Validated (nuance)</t>
         </is>
       </c>
     </row>
@@ -1862,9 +1856,9 @@
           <t>"Each agent can have a dedicated Microsoft Entra identity, enabling secure, scoped access to resources and APIs without sharing credentials."</t>
         </is>
       </c>
-      <c r="H33" s="9" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>Validated (nuance)</t>
         </is>
       </c>
     </row>
@@ -1904,9 +1898,9 @@
           <t>"Log Analytics - A flexible log search and analytics tool ... analysis of raw logs generated by an Azure resource."</t>
         </is>
       </c>
-      <c r="H34" s="9" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>Validated (nuance)</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1942,7 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1984,7 @@
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2026,7 @@
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -2072,9 +2066,9 @@
           <t>"Foundry offers a comprehensive catalog of AI models. The catalog includes over 10,000 models"</t>
         </is>
       </c>
-      <c r="H38" s="9" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>Validated (nuance)</t>
         </is>
       </c>
     </row>
@@ -2111,12 +2105,12 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>"Managed Compute</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>GPU</t>
+          <t>"Managed Compute | GPU | Price/1 Compute Hour | Managed A100 80G Global | $4"</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>Validated (absence)</t>
         </is>
       </c>
     </row>
@@ -2156,9 +2150,9 @@
           <t>"A skill is a SKILL.md file that you author once and store centrally in Foundry through the versioned Skills API."</t>
         </is>
       </c>
-      <c r="H40" s="9" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>Validated (nuance)</t>
         </is>
       </c>
     </row>
@@ -2198,9 +2192,9 @@
           <t>"a unified management interface that provides visibility, governance, and control for AI agents, models, and tools across your Foundry enterprise"</t>
         </is>
       </c>
-      <c r="H41" s="9" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>Validated (nuance)</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2236,7 @@
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -2285,7 +2279,7 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2321,7 @@
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2363,7 @@
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2405,7 @@
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2447,7 @@
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2489,7 @@
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -2535,9 +2529,9 @@
           <t>"A secure, serverless runtime environment purpose-built for deploying and scaling dynamic AI agents and tools."</t>
         </is>
       </c>
-      <c r="H49" s="9" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>Validated (nuance)</t>
         </is>
       </c>
     </row>
@@ -2577,9 +2571,9 @@
           <t>"A fast and secure cloud-based browser runtime environment"</t>
         </is>
       </c>
-      <c r="H50" s="9" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>Validated (nuance)</t>
         </is>
       </c>
     </row>
@@ -2619,9 +2613,9 @@
           <t>"any foundation model in or outside of Amazon Bedrock including OpenAI, Google's Gemini, Anthropic's Claude, Amazon Nova, Meta Llama, and Mistral models"</t>
         </is>
       </c>
-      <c r="H51" s="10" t="inlineStr">
-        <is>
-          <t>CONTRADICTED</t>
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>Validated (corrected)</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2657,7 @@
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -2705,7 +2699,7 @@
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -2745,9 +2739,9 @@
           <t>"AgentCore Registry works with any MCP Server, Agent, Skill or Custom Resource, deployed on AWS, On-Prem or on any other Cloud environment."</t>
         </is>
       </c>
-      <c r="H54" s="9" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>Validated (nuance)</t>
         </is>
       </c>
     </row>
@@ -2789,7 +2783,7 @@
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2826,7 @@
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2868,7 @@
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -2914,9 +2908,9 @@
           <t>"sensitive data can be stored in local files such as Markdown or JSON. If these files are not encrypted"</t>
         </is>
       </c>
-      <c r="H58" s="9" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>Validated (nuance)</t>
         </is>
       </c>
     </row>
@@ -2958,7 +2952,7 @@
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -2998,9 +2992,9 @@
           <t>"OpenClaw may execute multiple actions across systems without clear logging or oversight, which results in no visibility"</t>
         </is>
       </c>
-      <c r="H60" s="9" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>Validated (nuance)</t>
         </is>
       </c>
     </row>
@@ -3040,9 +3034,9 @@
           <t>"Not enterprise. Not hosted. Infrastructure you control."</t>
         </is>
       </c>
-      <c r="H61" s="9" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>Validated (nuance)</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3078,7 @@
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3120,7 @@
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3162,7 @@
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -3208,9 +3202,9 @@
           <t>"Bring hosted, subscription-backed, gateway, or local models."</t>
         </is>
       </c>
-      <c r="H65" s="9" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>Validated (nuance)</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3246,7 @@
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3288,7 @@
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3330,7 @@
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -3377,9 +3371,9 @@
           <t>"Before executing any command, Hermes checks it against a curated list of dangerous patterns."</t>
         </is>
       </c>
-      <c r="H69" s="9" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>Validated (nuance)</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3415,7 @@
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3457,7 @@
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3499,7 @@
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -3547,7 +3541,7 @@
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -3589,7 +3583,7 @@
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -3631,7 +3625,7 @@
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3667,7 @@
       </c>
       <c r="H76" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3709,7 @@
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -3755,9 +3749,9 @@
           <t>"You need at least one way to connect to an LLM."</t>
         </is>
       </c>
-      <c r="H78" s="9" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="H78" s="7" t="inlineStr">
+        <is>
+          <t>Validated (nuance)</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3793,7 @@
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -3841,7 +3835,7 @@
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -3883,7 +3877,7 @@
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -3924,9 +3918,9 @@
           <t>"However, encrypting other data at rest is the responsibility of the user."</t>
         </is>
       </c>
-      <c r="H82" s="9" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>Validated (nuance)</t>
         </is>
       </c>
     </row>
@@ -3966,9 +3960,9 @@
           <t>"Protect against SSRF attacks to control which hosts and IP ranges workflow nodes can connect to."</t>
         </is>
       </c>
-      <c r="H83" s="10" t="inlineStr">
-        <is>
-          <t>CONTRADICTED</t>
+      <c r="H83" s="9" t="inlineStr">
+        <is>
+          <t>Validated (corrected)</t>
         </is>
       </c>
     </row>
@@ -4010,7 +4004,7 @@
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -4050,9 +4044,9 @@
           <t>"Custom roles (instance and project) are available on: ... Self-hosted: Enterprise"</t>
         </is>
       </c>
-      <c r="H85" s="9" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t>Validated (nuance)</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4088,7 @@
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -4134,9 +4128,9 @@
           <t>"Project roles are available on: ... Self-hosted: Registered Community, Business, Enterprise"</t>
         </is>
       </c>
-      <c r="H87" s="9" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>Validated (nuance)</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4172,7 @@
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -4218,9 +4212,9 @@
           <t>"the entire workflow runs locally without any internet connection. This is ideal for air-gapped environments"</t>
         </is>
       </c>
-      <c r="H89" s="9" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>Validated (nuance)</t>
         </is>
       </c>
     </row>
@@ -4262,7 +4256,7 @@
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -4304,7 +4298,7 @@
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4340,7 @@
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -4388,7 +4382,7 @@
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>SUPPORTED</t>
+          <t>Validated</t>
         </is>
       </c>
     </row>
@@ -4428,9 +4422,9 @@
           <t>"dedicated support is supported only in our Enterprise plan."</t>
         </is>
       </c>
-      <c r="H94" s="9" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="H94" s="7" t="inlineStr">
+        <is>
+          <t>Validated (nuance)</t>
         </is>
       </c>
     </row>
@@ -4542,149 +4536,173 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>How to read this sheet</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr"/>
+      <c r="A2" s="11" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>One row per competitor capability shown on the AgentZ Comparison section. 7 vendors x 13 capabilities.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Rating on site: Built in = solid mark; Partial = ring; Not available = ghost mark.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Source: a public page (vendor doc, pricing page, or security report) that a skeptical buyer can open.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Verbatim evidence: an exact quote pulled from that page on 21 August 2026.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Verdict vs note: SUPPORTED = source backs the note. PARTIAL = broadly right, wording softened.</t>
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Status (site vs source): every cell now agrees with its source. No cell contradicts it.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   NOT FOUND = a claim of absence with no page that documents the feature either way.</t>
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Validated = the source backs the mark and note directly.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   CONTRADICTED = the source disagreed; the site was corrected (see below).</t>
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Validated (nuance) = broadly right; the note is worded to match the source exactly.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr"/>
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Validated (absence) = a 'not available' claim, and no vendor page documents the feature either way.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>Corrections made after re-verification (major flags)</t>
+          <t xml:space="preserve">   Validated (corrected) = the source once disagreed; the site was changed to match it (see below).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>LangGraph, Air-gapped: was 'Not available'. LangSmith documents air-gapped self-hosted on Enterprise. Now Partial.</t>
-        </is>
-      </c>
+      <c r="A12" s="11" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>AWS, Model agnostic: was 'Partial (Bedrock only)'. AgentCore runs any model in or outside Bedrock. Now Built in.</t>
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Four cells the source contradicted, now corrected on the site and validated</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>n8n, Network egress: was 'Not available'. n8n ships SSRF host filtering. Now Partial (opt-in).</t>
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>LangGraph, Air-gapped: was 'Not available'. LangSmith documents air-gapped self-hosted on Enterprise. Now Partial. RESOLVED.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>CrewAI, Dynamic skill creation: was 'Not available'. Crew Studio builds no-code workflows from a prompt. Now Partial.</t>
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>AWS, Model agnostic: was 'Partial (Bedrock only)'. AgentCore runs any model in or outside Bedrock. Now Built in. RESOLVED.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>Microsoft, Zero trust: note reworded. Foundry guardrails do fire per tool call, so 'not per action' was dropped.</t>
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>n8n, Network egress: was 'Not available'. n8n ships SSRF host filtering. Now Partial (opt-in). RESOLVED.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>LangGraph, Full audit trail: note reworded. LangSmith has an Enterprise audit-logs feature.</t>
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Microsoft, Zero trust: note said 'not per action', but guardrails fire per tool call. Note corrected. RESOLVED.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>Hermes, Zero trust: note reworded. Default mode auto-approves low-risk calls; it does not prompt on every call.</t>
-        </is>
-      </c>
+      <c r="A18" s="11" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr"/>
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Notes tightened at the same time (mark unchanged, wording made to match the source)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
+          <t>CrewAI, Dynamic skill creation: bumped to Partial. Crew Studio builds no-code workflows from a prompt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>LangGraph, Full audit trail: note reworded. LangSmith has an Enterprise audit-logs feature.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>Hermes, Zero trust: note reworded. Default mode auto-approves low-risk calls; it does not prompt on every call.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
           <t>Source-accuracy flag for the marketing doc (not the site)</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>marketing/competitor-comparison.md cites 'ClawJacked, CVE-2026-25253' for OpenClaw. The Oasis Security blog</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>confirms the takeover vulnerability and names fix version 2026.2.25, but does not state that CVE id. Verify or drop the number.</t>
         </is>
